--- a/backend/data/financials_by_company/1HENS.MI.xlsx
+++ b/backend/data/financials_by_company/1HENS.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,550 +647,687 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>198000</v>
+        <v>2620000</v>
       </c>
       <c r="C2" t="n">
-        <v>0.099</v>
+        <v>0.262</v>
       </c>
       <c r="D2" t="n">
-        <v>377000000</v>
+        <v>243000000</v>
       </c>
       <c r="E2" t="n">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
       <c r="F2" t="n">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
       <c r="G2" t="n">
-        <v>108000000</v>
+        <v>63000000</v>
       </c>
       <c r="H2" t="n">
-        <v>162000000</v>
+        <v>126000000</v>
       </c>
       <c r="I2" t="n">
-        <v>1732000000</v>
+        <v>1144000000</v>
       </c>
       <c r="J2" t="n">
-        <v>379000000</v>
+        <v>253000000</v>
       </c>
       <c r="K2" t="n">
-        <v>217000000</v>
+        <v>127000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-73000000</v>
+        <v>-43000000</v>
       </c>
       <c r="M2" t="n">
-        <v>100000000</v>
+        <v>42000000</v>
       </c>
       <c r="N2" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>55620000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1357000000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-43000000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>117000000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>213000000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="AL2" t="n">
         <v>31000000</v>
       </c>
-      <c r="O2" t="n">
-        <v>106198000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2056000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>116000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>116000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="V2" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>106000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>105000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>117000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-73000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>31000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>185000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>324000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>32000000</v>
-      </c>
       <c r="AM2" t="n">
-        <v>290000000</v>
+        <v>182000000</v>
       </c>
       <c r="AN2" t="n">
-        <v>128000000</v>
+        <v>99000000</v>
       </c>
       <c r="AO2" t="n">
-        <v>162000000</v>
+        <v>83000000</v>
       </c>
       <c r="AP2" t="n">
-        <v>509000000</v>
+        <v>330000000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1732000000</v>
+        <v>1144000000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2241000000</v>
+        <v>1474000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2241000000</v>
+        <v>1474000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1152000</v>
+        <v>1146000</v>
       </c>
       <c r="C3" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="D3" t="n">
-        <v>296000000</v>
+        <v>274000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-3000000</v>
+        <v>3000000</v>
       </c>
       <c r="F3" t="n">
-        <v>-3000000</v>
+        <v>3000000</v>
       </c>
       <c r="G3" t="n">
-        <v>56000000</v>
+        <v>78000000</v>
       </c>
       <c r="H3" t="n">
-        <v>117000000</v>
+        <v>103000000</v>
       </c>
       <c r="I3" t="n">
-        <v>1427000000</v>
+        <v>1314000000</v>
       </c>
       <c r="J3" t="n">
-        <v>293000000</v>
+        <v>277000000</v>
       </c>
       <c r="K3" t="n">
-        <v>176000000</v>
+        <v>174000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-66000000</v>
+        <v>-35000000</v>
       </c>
       <c r="M3" t="n">
-        <v>82000000</v>
+        <v>44000000</v>
       </c>
       <c r="N3" t="n">
-        <v>18000000</v>
+        <v>9000000</v>
       </c>
       <c r="O3" t="n">
-        <v>57848000</v>
+        <v>76146000</v>
       </c>
       <c r="P3" t="n">
-        <v>56000000</v>
+        <v>78000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1685000000</v>
+        <v>1548000000</v>
       </c>
       <c r="R3" t="n">
-        <v>106000000</v>
+        <v>105000000</v>
       </c>
       <c r="S3" t="n">
-        <v>106000000</v>
+        <v>105000000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="V3" t="n">
-        <v>56000000</v>
+        <v>78000000</v>
       </c>
       <c r="W3" t="n">
-        <v>56000000</v>
+        <v>78000000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>56000000</v>
+        <v>78000000</v>
       </c>
       <c r="Z3" t="n">
         <v>-2000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>58000000</v>
+        <v>80000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>58000000</v>
+        <v>81000000</v>
       </c>
       <c r="AC3" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-35000000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>234000000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AL3" t="n">
         <v>36000000</v>
       </c>
-      <c r="AD3" t="n">
-        <v>94000000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-66000000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>82000000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>161000000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>258000000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>30000000</v>
-      </c>
       <c r="AM3" t="n">
-        <v>229000000</v>
+        <v>199000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>111000000</v>
+        <v>107000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>118000000</v>
+        <v>92000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>419000000</v>
+        <v>394000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1427000000</v>
+        <v>1314000000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1846000000</v>
+        <v>1708000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1846000000</v>
+        <v>1708000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1146000</v>
+        <v>-1152000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.382</v>
+        <v>0.384</v>
       </c>
       <c r="D4" t="n">
-        <v>274000000</v>
+        <v>296000000</v>
       </c>
       <c r="E4" t="n">
-        <v>3000000</v>
+        <v>-3000000</v>
       </c>
       <c r="F4" t="n">
-        <v>3000000</v>
+        <v>-3000000</v>
       </c>
       <c r="G4" t="n">
-        <v>78000000</v>
+        <v>56000000</v>
       </c>
       <c r="H4" t="n">
-        <v>103000000</v>
+        <v>117000000</v>
       </c>
       <c r="I4" t="n">
-        <v>1314000000</v>
+        <v>1427000000</v>
       </c>
       <c r="J4" t="n">
-        <v>277000000</v>
+        <v>293000000</v>
       </c>
       <c r="K4" t="n">
-        <v>174000000</v>
+        <v>176000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-35000000</v>
+        <v>-66000000</v>
       </c>
       <c r="M4" t="n">
-        <v>44000000</v>
+        <v>82000000</v>
       </c>
       <c r="N4" t="n">
-        <v>9000000</v>
+        <v>18000000</v>
       </c>
       <c r="O4" t="n">
-        <v>76146000</v>
+        <v>57848000</v>
       </c>
       <c r="P4" t="n">
-        <v>78000000</v>
+        <v>56000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1548000000</v>
+        <v>1685000000</v>
       </c>
       <c r="R4" t="n">
-        <v>105000000</v>
+        <v>106000000</v>
       </c>
       <c r="S4" t="n">
-        <v>105000000</v>
+        <v>106000000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="V4" t="n">
-        <v>78000000</v>
+        <v>56000000</v>
       </c>
       <c r="W4" t="n">
-        <v>78000000</v>
+        <v>56000000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>78000000</v>
+        <v>56000000</v>
       </c>
       <c r="Z4" t="n">
         <v>-2000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>80000000</v>
+        <v>58000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>81000000</v>
+        <v>58000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>49000000</v>
+        <v>36000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>130000000</v>
+        <v>94000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-35000000</v>
+        <v>-66000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>44000000</v>
+        <v>82000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>9000000</v>
+        <v>18000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>160000000</v>
+        <v>161000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>234000000</v>
+        <v>258000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>20000000</v>
+        <v>21000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>36000000</v>
+        <v>30000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>199000000</v>
+        <v>229000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>107000000</v>
+        <v>111000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>92000000</v>
+        <v>118000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>394000000</v>
+        <v>419000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1314000000</v>
+        <v>1427000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1708000000</v>
+        <v>1846000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1708000000</v>
+        <v>1846000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2620000</v>
+        <v>205128.205128</v>
       </c>
       <c r="C5" t="n">
-        <v>0.262</v>
+        <v>0.102564</v>
       </c>
       <c r="D5" t="n">
-        <v>243000000</v>
+        <v>377000000</v>
       </c>
       <c r="E5" t="n">
-        <v>10000000</v>
+        <v>2000000</v>
       </c>
       <c r="F5" t="n">
-        <v>10000000</v>
+        <v>2000000</v>
       </c>
       <c r="G5" t="n">
-        <v>63000000</v>
+        <v>108000000</v>
       </c>
       <c r="H5" t="n">
-        <v>126000000</v>
+        <v>162000000</v>
       </c>
       <c r="I5" t="n">
-        <v>1144000000</v>
+        <v>1732000000</v>
       </c>
       <c r="J5" t="n">
-        <v>253000000</v>
+        <v>379000000</v>
       </c>
       <c r="K5" t="n">
+        <v>217000000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-73000000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>106205128.205128</v>
+      </c>
+      <c r="P5" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2056000000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>116000000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>116000000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="V5" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>106000000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>117000000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-73000000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>185000000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>324000000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>290000000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>128000000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>162000000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>509000000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1732000000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2241000000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2241000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-644000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="D6" t="n">
+        <v>416000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>181000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1930000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>414000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>233000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-85000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>106000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>90356000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2231000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>116000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>116000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="V6" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>41000000</v>
+      </c>
+      <c r="AD6" t="n">
         <v>127000000</v>
       </c>
-      <c r="L5" t="n">
-        <v>-43000000</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="AE6" t="n">
+        <v>-85000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>106000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>223000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>301000000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="AL6" t="n">
         <v>42000000</v>
       </c>
-      <c r="N5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>55620000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>63000000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1357000000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>105000000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>105000000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V5" t="n">
-        <v>63000000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>63000000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>63000000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>63000000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>63000000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-43000000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>117000000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>213000000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>31000000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>182000000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>99000000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>83000000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>330000000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1144000000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1474000000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1474000000</v>
+      <c r="AM6" t="n">
+        <v>279000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>132000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>147000000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>524000000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1930000000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2454000000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2454000000</v>
       </c>
     </row>
   </sheetData>
@@ -1204,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD5"/>
+  <dimension ref="A1:CF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,388 +1750,252 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>Defined Pension Benefit</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>115500000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>115500000</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>361000000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1375000000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-910000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1966000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>524000000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-910000000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>281000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>872000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1944000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>886000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>872000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>245000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>474000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>116000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>116000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3810000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1927000000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>31000000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>123000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1328000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>256000000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1072000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>418000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1883000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>47000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>66000000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>257000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>643000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>97000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>546000000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4696000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2289000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>259000000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>9000000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>1782000000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>667000000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1115000000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>452000000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-168000000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>620000000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>79000000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>269000000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>244000000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>28000000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>2407000000</v>
-      </c>
-      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
         <v>6000000</v>
       </c>
-      <c r="BO2" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>83000000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>719000000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>304000000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>392000000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>386000000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>47000000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>426000000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>436000000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>734000000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>733000000</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>210000000</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>523000000</v>
-      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>115500000</v>
+        <v>105000000</v>
       </c>
       <c r="D3" t="n">
-        <v>115500000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>105000000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>170000000</v>
+      </c>
       <c r="F3" t="n">
-        <v>854000000</v>
+        <v>788000000</v>
       </c>
       <c r="G3" t="n">
-        <v>-236000000</v>
+        <v>-438000000</v>
       </c>
       <c r="H3" t="n">
-        <v>1465000000</v>
+        <v>1234000000</v>
       </c>
       <c r="I3" t="n">
-        <v>685000000</v>
+        <v>441000000</v>
       </c>
       <c r="J3" t="n">
-        <v>-236000000</v>
+        <v>-438000000</v>
       </c>
       <c r="K3" t="n">
-        <v>211000000</v>
+        <v>158000000</v>
       </c>
       <c r="L3" t="n">
-        <v>822000000</v>
+        <v>604000000</v>
       </c>
       <c r="M3" t="n">
-        <v>1443000000</v>
+        <v>1223000000</v>
       </c>
       <c r="N3" t="n">
-        <v>838000000</v>
+        <v>617000000</v>
       </c>
       <c r="O3" t="n">
-        <v>16000000</v>
+        <v>13000000</v>
       </c>
       <c r="P3" t="n">
-        <v>822000000</v>
+        <v>604000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>62000000</v>
+        <v>-55000000</v>
       </c>
       <c r="R3" t="n">
-        <v>613000000</v>
+        <v>472000000</v>
       </c>
       <c r="S3" t="n">
-        <v>116000000</v>
+        <v>105000000</v>
       </c>
       <c r="T3" t="n">
-        <v>116000000</v>
+        <v>105000000</v>
       </c>
       <c r="U3" t="n">
-        <v>2741000000</v>
+        <v>2362000000</v>
       </c>
       <c r="V3" t="n">
-        <v>1271000000</v>
+        <v>1159000000</v>
       </c>
       <c r="W3" t="n">
         <v>-1000000</v>
       </c>
       <c r="X3" t="n">
-        <v>10000000</v>
+        <v>3000000</v>
       </c>
       <c r="Y3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>94000000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>759000000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>619000000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>282000000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1203000000</v>
+      </c>
+      <c r="AG3" t="n">
         <v>14000000</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>79000000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>812000000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>191000000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>621000000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>357000000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1470000000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>17000000</v>
-      </c>
       <c r="AH3" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="AK3" t="n">
         <v>42000000</v>
       </c>
-      <c r="AI3" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AL3" t="n">
+        <v>181000000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>446000000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>379000000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2979000000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1335000000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
         <v>22000000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>211000000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>571000000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>114000000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>457000000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3579000000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1424000000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>25000000</v>
       </c>
       <c r="AV3" t="n">
         <v>1000000</v>
@@ -2003,240 +2004,244 @@
         <v>1000000</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
+        <v>15000000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="n">
+        <v>6000000</v>
+      </c>
       <c r="BB3" t="n">
-        <v>1058000000</v>
+        <v>1042000000</v>
       </c>
       <c r="BC3" t="n">
-        <v>400000000</v>
+        <v>384000000</v>
       </c>
       <c r="BD3" t="n">
         <v>658000000</v>
       </c>
       <c r="BE3" t="n">
-        <v>330000000</v>
+        <v>261000000</v>
       </c>
       <c r="BF3" t="n">
-        <v>-142000000</v>
+        <v>-120000000</v>
       </c>
       <c r="BG3" t="n">
-        <v>472000000</v>
+        <v>381000000</v>
       </c>
       <c r="BH3" t="n">
-        <v>38000000</v>
+        <v>29000000</v>
       </c>
       <c r="BI3" t="n">
-        <v>231000000</v>
+        <v>200000000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>184000000</v>
+        <v>135000000</v>
       </c>
       <c r="BK3" t="n">
-        <v>19000000</v>
+        <v>17000000</v>
       </c>
       <c r="BL3" t="n">
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>2155000000</v>
+        <v>1644000000</v>
       </c>
       <c r="BN3" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
       <c r="BO3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>109000000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>516000000</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>247000000</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>237000000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>191000000</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>323000000</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>332000000</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>462000000</v>
+      </c>
+      <c r="CA3" t="n">
         <v>2000000</v>
       </c>
-      <c r="BP3" t="n">
-        <v>88000000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>625000000</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>278000000</v>
-      </c>
-      <c r="BT3" t="n">
+      <c r="CB3" t="n">
+        <v>460000000</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="CD3" t="n">
         <v>310000000</v>
       </c>
-      <c r="BU3" t="n">
-        <v>212000000</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>382000000</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>-11000000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>393000000</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>803000000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>802000000</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>238000000</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>564000000</v>
-      </c>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
-        <v>105000000</v>
+        <v>115500000</v>
       </c>
       <c r="D4" t="n">
-        <v>105000000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>170000000</v>
-      </c>
+        <v>115500000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>788000000</v>
+        <v>854000000</v>
       </c>
       <c r="G4" t="n">
-        <v>-438000000</v>
+        <v>-236000000</v>
       </c>
       <c r="H4" t="n">
-        <v>1234000000</v>
+        <v>1465000000</v>
       </c>
       <c r="I4" t="n">
-        <v>441000000</v>
+        <v>685000000</v>
       </c>
       <c r="J4" t="n">
-        <v>-438000000</v>
+        <v>-236000000</v>
       </c>
       <c r="K4" t="n">
-        <v>158000000</v>
+        <v>211000000</v>
       </c>
       <c r="L4" t="n">
-        <v>604000000</v>
+        <v>822000000</v>
       </c>
       <c r="M4" t="n">
-        <v>1223000000</v>
+        <v>1443000000</v>
       </c>
       <c r="N4" t="n">
-        <v>617000000</v>
+        <v>838000000</v>
       </c>
       <c r="O4" t="n">
-        <v>13000000</v>
+        <v>16000000</v>
       </c>
       <c r="P4" t="n">
-        <v>604000000</v>
+        <v>822000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-55000000</v>
+        <v>62000000</v>
       </c>
       <c r="R4" t="n">
-        <v>472000000</v>
+        <v>613000000</v>
       </c>
       <c r="S4" t="n">
-        <v>105000000</v>
+        <v>116000000</v>
       </c>
       <c r="T4" t="n">
-        <v>105000000</v>
+        <v>116000000</v>
       </c>
       <c r="U4" t="n">
-        <v>2362000000</v>
+        <v>2741000000</v>
       </c>
       <c r="V4" t="n">
-        <v>1159000000</v>
+        <v>1271000000</v>
       </c>
       <c r="W4" t="n">
         <v>-1000000</v>
       </c>
       <c r="X4" t="n">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>11000000</v>
+        <v>14000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>11000000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>94000000</v>
+        <v>79000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>759000000</v>
+        <v>812000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>140000000</v>
+        <v>191000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>619000000</v>
+        <v>621000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>282000000</v>
+        <v>357000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1203000000</v>
+        <v>1470000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>14000000</v>
+        <v>17000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>29000000</v>
+        <v>42000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11000000</v>
+        <v>22000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>42000000</v>
+        <v>45000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>181000000</v>
+        <v>211000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>446000000</v>
+        <v>571000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>67000000</v>
+        <v>114000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>379000000</v>
+        <v>457000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2979000000</v>
+        <v>3579000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1335000000</v>
+        <v>1424000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>6000000</v>
+        <v>9000000</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>22000000</v>
+        <v>25000000</v>
       </c>
       <c r="AV4" t="n">
         <v>1000000</v>
@@ -2245,345 +2250,597 @@
         <v>1000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="n">
-        <v>6000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>1042000000</v>
+        <v>1058000000</v>
       </c>
       <c r="BC4" t="n">
-        <v>384000000</v>
+        <v>400000000</v>
       </c>
       <c r="BD4" t="n">
         <v>658000000</v>
       </c>
       <c r="BE4" t="n">
-        <v>261000000</v>
+        <v>330000000</v>
       </c>
       <c r="BF4" t="n">
-        <v>-120000000</v>
+        <v>-142000000</v>
       </c>
       <c r="BG4" t="n">
-        <v>381000000</v>
+        <v>472000000</v>
       </c>
       <c r="BH4" t="n">
-        <v>29000000</v>
+        <v>38000000</v>
       </c>
       <c r="BI4" t="n">
-        <v>200000000</v>
+        <v>231000000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>135000000</v>
+        <v>184000000</v>
       </c>
       <c r="BK4" t="n">
-        <v>17000000</v>
+        <v>19000000</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1644000000</v>
+        <v>2155000000</v>
       </c>
       <c r="BN4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
       <c r="BO4" t="n">
-        <v>8000000</v>
+        <v>2000000</v>
       </c>
       <c r="BP4" t="n">
-        <v>109000000</v>
+        <v>88000000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>516000000</v>
+        <v>625000000</v>
       </c>
       <c r="BR4" t="n">
-        <v>32000000</v>
+        <v>37000000</v>
       </c>
       <c r="BS4" t="n">
-        <v>247000000</v>
+        <v>278000000</v>
       </c>
       <c r="BT4" t="n">
-        <v>237000000</v>
+        <v>310000000</v>
       </c>
       <c r="BU4" t="n">
-        <v>191000000</v>
+        <v>212000000</v>
       </c>
       <c r="BV4" t="n">
-        <v>30000000</v>
+        <v>37000000</v>
       </c>
       <c r="BW4" t="n">
-        <v>323000000</v>
+        <v>382000000</v>
       </c>
       <c r="BX4" t="n">
-        <v>-9000000</v>
+        <v>-11000000</v>
       </c>
       <c r="BY4" t="n">
-        <v>332000000</v>
+        <v>393000000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>462000000</v>
+        <v>803000000</v>
       </c>
       <c r="CA4" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="CB4" t="n">
-        <v>460000000</v>
+        <v>802000000</v>
       </c>
       <c r="CC4" t="n">
-        <v>150000000</v>
+        <v>238000000</v>
       </c>
       <c r="CD4" t="n">
-        <v>310000000</v>
-      </c>
+        <v>564000000</v>
+      </c>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>105000000</v>
+        <v>115500000</v>
       </c>
       <c r="D5" t="n">
-        <v>105000000</v>
+        <v>115500000</v>
       </c>
       <c r="E5" t="n">
-        <v>259000000</v>
+        <v>361000000</v>
       </c>
       <c r="F5" t="n">
-        <v>943000000</v>
+        <v>1375000000</v>
       </c>
       <c r="G5" t="n">
-        <v>-637000000</v>
+        <v>-910000000</v>
       </c>
       <c r="H5" t="n">
-        <v>1194000000</v>
+        <v>1966000000</v>
       </c>
       <c r="I5" t="n">
-        <v>374000000</v>
+        <v>524000000</v>
       </c>
       <c r="J5" t="n">
-        <v>-637000000</v>
+        <v>-910000000</v>
       </c>
       <c r="K5" t="n">
-        <v>155000000</v>
+        <v>281000000</v>
       </c>
       <c r="L5" t="n">
-        <v>406000000</v>
+        <v>872000000</v>
       </c>
       <c r="M5" t="n">
-        <v>1028000000</v>
+        <v>1944000000</v>
       </c>
       <c r="N5" t="n">
-        <v>417000000</v>
+        <v>886000000</v>
       </c>
       <c r="O5" t="n">
-        <v>11000000</v>
+        <v>14000000</v>
       </c>
       <c r="P5" t="n">
-        <v>406000000</v>
+        <v>872000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-171000000</v>
+        <v>245000000</v>
       </c>
       <c r="R5" t="n">
-        <v>537000000</v>
+        <v>474000000</v>
       </c>
       <c r="S5" t="n">
-        <v>105000000</v>
+        <v>116000000</v>
       </c>
       <c r="T5" t="n">
-        <v>105000000</v>
+        <v>116000000</v>
       </c>
       <c r="U5" t="n">
-        <v>2539000000</v>
+        <v>3810000000</v>
       </c>
       <c r="V5" t="n">
-        <v>1284000000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>1927000000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1000000</v>
+      </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>10000000</v>
+        <v>15000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>12000000</v>
+        <v>31000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>4000000</v>
+        <v>123000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>761000000</v>
+        <v>1328000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>139000000</v>
+        <v>256000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>622000000</v>
+        <v>1072000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>497000000</v>
+        <v>418000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1255000000</v>
+        <v>1883000000</v>
       </c>
       <c r="AG5" t="n">
-        <v>9000000</v>
+        <v>19000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>182000000</v>
+        <v>47000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>16000000</v>
+        <v>25000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>166000000</v>
+        <v>22000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>39000000</v>
+        <v>66000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>188000000</v>
+        <v>257000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>327000000</v>
+        <v>643000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>58000000</v>
+        <v>97000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>269000000</v>
+        <v>546000000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2956000000</v>
+        <v>4696000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1326000000</v>
+        <v>2289000000</v>
       </c>
       <c r="AR5" t="n">
         <v>1000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>11000000</v>
+        <v>1000000</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>1782000000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>667000000</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1115000000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-168000000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>79000000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2407000000</v>
+      </c>
+      <c r="BN5" t="n">
         <v>6000000</v>
       </c>
-      <c r="AV5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1043000000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>385000000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>658000000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>249000000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-100000000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>349000000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>180000000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>135000000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1629000000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>2000000</v>
-      </c>
       <c r="BO5" t="n">
-        <v>2000000</v>
+        <v>5000000</v>
       </c>
       <c r="BP5" t="n">
-        <v>147000000</v>
+        <v>83000000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>444000000</v>
+        <v>719000000</v>
       </c>
       <c r="BR5" t="n">
-        <v>26000000</v>
+        <v>23000000</v>
       </c>
       <c r="BS5" t="n">
-        <v>231000000</v>
+        <v>304000000</v>
       </c>
       <c r="BT5" t="n">
-        <v>187000000</v>
+        <v>392000000</v>
       </c>
       <c r="BU5" t="n">
-        <v>175000000</v>
+        <v>386000000</v>
       </c>
       <c r="BV5" t="n">
-        <v>19000000</v>
+        <v>47000000</v>
       </c>
       <c r="BW5" t="n">
-        <v>309000000</v>
+        <v>426000000</v>
       </c>
       <c r="BX5" t="n">
         <v>-10000000</v>
       </c>
       <c r="BY5" t="n">
-        <v>319000000</v>
+        <v>436000000</v>
       </c>
       <c r="BZ5" t="n">
+        <v>734000000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>733000000</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>210000000</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>523000000</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>264000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>115500000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>115500000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>250000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1634000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-828000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2174000000</v>
+      </c>
+      <c r="I6" t="n">
         <v>531000000</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="J6" t="n">
+        <v>-828000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>451000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>991000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2154000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1002000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>991000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>309000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>439000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>116000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>116000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4425000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2091000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>34000000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>166000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1579000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>416000000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1163000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>287000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2334000000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>260000000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>729000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>591000000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5427000000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2562000000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>1819000000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>702000000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1117000000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>655000000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-194000000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>849000000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>93000000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>408000000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2865000000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="BO6" t="n">
         <v>2000000</v>
       </c>
-      <c r="CB5" t="n">
-        <v>529000000</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>529000000</v>
+      <c r="BP6" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>878000000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>364000000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>486000000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>466000000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>436000000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>442000000</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>934000000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>933000000</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>280000000</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>653000000</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>313000000</v>
       </c>
     </row>
   </sheetData>
@@ -2597,7 +2854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2816,521 +3073,621 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Dividends Received Cfi</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Net Investment Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Sale Of Investment</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>112000000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>450000000</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>-199000000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>733000000</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>-14000000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
         <v>1000000</v>
       </c>
-      <c r="I2" t="n">
-        <v>802000000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-3000000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-67000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>367000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-7000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-46000000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>450000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-745000000</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
         <v>-1000000</v>
       </c>
-      <c r="X2" t="n">
-        <v>-547000000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-547000000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-197000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-199000000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>311000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-18000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-66000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>28000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>78000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>69000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-103000000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-11000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>53000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>162000000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>162000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>106000000</v>
-      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>152000000</v>
+        <v>149000000</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-150000000</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>241000000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-115000000</v>
+        <v>-95000000</v>
       </c>
       <c r="G3" t="n">
-        <v>802000000</v>
+        <v>460000000</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>460000000</v>
+        <v>529000000</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="K3" t="n">
-        <v>342000000</v>
+        <v>-71000000</v>
       </c>
       <c r="L3" t="n">
-        <v>197000000</v>
+        <v>-214000000</v>
       </c>
       <c r="M3" t="n">
-        <v>10000000</v>
+        <v>-19000000</v>
       </c>
       <c r="N3" t="n">
-        <v>-32000000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>-26000000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-26000000</v>
+      </c>
       <c r="P3" t="n">
-        <v>241000000</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>241000000</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-150000000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-150000000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-150000000</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-122000000</v>
-      </c>
-      <c r="W3" t="n">
+        <v>-101000000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-95000000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-95000000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1000000</v>
       </c>
-      <c r="X3" t="n">
-        <v>-9000000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-114000000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-115000000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>267000000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-27000000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9000000</v>
-      </c>
       <c r="AG3" t="n">
-        <v>-44000000</v>
+        <v>-26000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>46000000</v>
+        <v>17000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>117000000</v>
+        <v>17000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78000000</v>
+        <v>110000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-128000000</v>
+        <v>-75000000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-66000000</v>
+        <v>-13000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>55000000</v>
+        <v>28000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>36000000</v>
+        <v>49000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>117000000</v>
+        <v>103000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>117000000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-1000000</v>
-      </c>
+        <v>103000000</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>58000000</v>
-      </c>
+        <v>80000000</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>149000000</v>
+        <v>152000000</v>
       </c>
       <c r="C4" t="n">
-        <v>-150000000</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>241000000</v>
       </c>
       <c r="F4" t="n">
-        <v>-95000000</v>
+        <v>-115000000</v>
       </c>
       <c r="G4" t="n">
-        <v>460000000</v>
+        <v>802000000</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>529000000</v>
+        <v>460000000</v>
       </c>
       <c r="J4" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-71000000</v>
+        <v>342000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-214000000</v>
+        <v>197000000</v>
       </c>
       <c r="M4" t="n">
-        <v>-19000000</v>
+        <v>10000000</v>
       </c>
       <c r="N4" t="n">
-        <v>-26000000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-26000000</v>
-      </c>
+        <v>-32000000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>241000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>241000000</v>
       </c>
       <c r="R4" t="n">
-        <v>-150000000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-150000000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-150000000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-101000000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>-122000000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1000000</v>
+      </c>
       <c r="X4" t="n">
-        <v>-6000000</v>
+        <v>-9000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-6000000</v>
+        <v>-10000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-95000000</v>
+        <v>-114000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-95000000</v>
+        <v>-115000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>244000000</v>
+        <v>267000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-11000000</v>
+        <v>-27000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000000</v>
+        <v>9000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-26000000</v>
+        <v>-44000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>17000000</v>
+        <v>46000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>17000000</v>
+        <v>117000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>110000000</v>
+        <v>78000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-75000000</v>
+        <v>-128000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-13000000</v>
+        <v>-66000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>28000000</v>
+        <v>55000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>49000000</v>
+        <v>36000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>103000000</v>
+        <v>117000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>103000000</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>117000000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1000000</v>
+      </c>
       <c r="AR4" t="n">
-        <v>80000000</v>
-      </c>
+        <v>58000000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
+        <v>112000000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-199000000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>733000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>802000000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-67000000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>367000000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-46000000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-745000000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-547000000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-547000000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-197000000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-199000000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>311000000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-18000000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-66000000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-103000000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>162000000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>162000000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>106000000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-220000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>-206000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>933000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>733000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K6" t="n">
         <v>197000000</v>
       </c>
-      <c r="C5" t="n">
-        <v>-210000000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-102000000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>529000000</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>645000000</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="L6" t="n">
+        <v>-20000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-58000000</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-220000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-233000000</v>
+      </c>
+      <c r="W6" t="n">
         <v>-1000000</v>
       </c>
-      <c r="K5" t="n">
-        <v>-115000000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-297000000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-84000000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-14000000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-14000000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-180000000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-180000000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-210000000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-117000000</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="X6" t="n">
+        <v>-30000000</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>-30000000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-205000000</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1000000</v>
       </c>
-      <c r="X5" t="n">
-        <v>-19000000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-19000000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-99000000</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AC6" t="n">
+        <v>-206000000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-31000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-69000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>328000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-169000000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>41000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>181000000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>181000000</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="AS6" t="n">
         <v>3000000</v>
       </c>
-      <c r="AC5" t="n">
-        <v>-102000000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>299000000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-9000000</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
-        <v>-36000000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>28000000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>107000000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-44000000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-22000000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>126000000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>126000000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>63000000</v>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3344,7 +3701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU2"/>
+  <dimension ref="A1:EQ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,590 +3872,570 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>pegRatio</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>pegRatio</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>messageBoardId</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>corporateActions</t>
+          <t>exchangeTimezoneName</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>regularMarketTime</t>
+          <t>exchangeTimezoneShortName</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
       <c r="EQ1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4115,10 +4452,8 @@
           <t>Taufkirchen</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>82024</t>
-        </is>
+      <c r="C2" t="n">
+        <v>82024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4175,7 +4510,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Christian  Ladurner', 'age': 48, 'title': 'CFO &amp; Member of Management Board', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 798651, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Lars  Immisch', 'age': 58, 'title': 'Executive Officer', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 812248, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Nicolas  Debove', 'title': 'Chief Operating Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Veronika  Endres', 'title': 'Head of Group Reporting &amp; Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Katja  Stadelmann', 'title': 'General Counsel', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Simona  Patap', 'title': 'Marketing Manager', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Stefan  Hess', 'age': 57, 'title': 'Head of Group Sales &amp; Account Management', 'yearBorn': 1968, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Temur  Karbassioun', 'title': 'Head of Customer Service', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Andreas  Hulle', 'title': 'Head of Optronics', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Werner  Stockburger', 'title': 'Head of Corporate College', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Oliver  Dorre', 'title': 'CEO &amp; Chairman of Management Board', 'fiscalYear': 2025, 'totalPay': 1484185, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Christian  Ladurner', 'age': 48, 'title': 'CFO &amp; Member of Management Board', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 798651, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Lars  Immisch', 'age': 58, 'title': 'Executive Officer', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 812248, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Nicolas  Debove', 'title': 'Chief Operating Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Inka  Tews', 'age': 54, 'title': 'Chief Human Resources Officer, Labour Director &amp; Member of Management Board', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Veronika  Endres', 'title': 'Head of Group Reporting &amp; Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Katja  Stadelmann', 'title': 'General Counsel', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Simona  Patap', 'title': 'Marketing Manager', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Stefan  Hess', 'age': 57, 'title': 'Head of Group Sales &amp; Account Management', 'yearBorn': 1968, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Temur  Karbassioun', 'title': 'Head of Customer Service', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4194,7 +4529,7 @@
         <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="V2" t="n">
         <v>1767139200</v>
@@ -4211,428 +4546,416 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>83.23999999999999</v>
+        <v>71.06</v>
       </c>
       <c r="AA2" t="n">
-        <v>81</v>
+        <v>72.36</v>
       </c>
       <c r="AB2" t="n">
-        <v>81</v>
+        <v>72.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>81</v>
+        <v>72.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>83.23999999999999</v>
+        <v>71.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>81</v>
+        <v>72.36</v>
       </c>
       <c r="AF2" t="n">
-        <v>81</v>
+        <v>72.36</v>
       </c>
       <c r="AG2" t="n">
-        <v>81</v>
+        <v>72.36</v>
       </c>
       <c r="AH2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>86.02298999999999</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>426</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>945</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>945</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>74.66</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8644019200</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8267490000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.381854</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>77.12439999999999</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>82.6675</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>0.55</v>
       </c>
-      <c r="AI2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="BA2" t="n">
+        <v>0.0077399383</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>9252875264</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.03912</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>61868750</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>115500000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.47919998</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>115500000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>8.244</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>9.078116</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>27.621</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-0.19742626</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BX2" t="n">
         <v>1779667200</v>
       </c>
-      <c r="AK2" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>77.943924</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>309</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>729</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>729</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>79.06</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9632700416</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9618840000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>117.9</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>117.9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>30.12</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3.7686622</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>77.18040000000001</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>83.54535</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.0066074007</v>
-      </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BZ2" t="n">
+        <v>74.84</v>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CB2" t="n">
+        <v>820000000</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>6.905</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>335000000</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1652999936</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>2556000000</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>167.139</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>21.876</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.02922</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.10305</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>541000000</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>265500000</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>498000000</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.21166</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.13106</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>-0.008059999999999999</v>
+      </c>
+      <c r="CT2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="BG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>10746749952</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0.03912</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>61868750</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>115500000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.47919998</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.39117</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>115500000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>8.244</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>10.116448</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>4.205</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>-0.17665678</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>1779667200</v>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="CD2" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CF2" t="n">
-        <v>820000000</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>6.905</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>335000000</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1652999936</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.193</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>2556000000</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>167.139</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>21.876</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0.02922</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.10305</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>541000000</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>265500000</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>498000000</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0.21166</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>0.13106</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>-0.008059999999999999</v>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>1HENS.MI</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>1HENS.MI</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CZ2" t="b">
+        <v>0</v>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DD2" t="b">
-        <v>0</v>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>1781874477</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>finmb_328775146</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>1780414142</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>7200000</v>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>finmb_328775146</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1715756400000</v>
       </c>
       <c r="DM2" t="n">
-        <v>7200000</v>
+        <v>3.7799988</v>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
+          <t>72.36 - 72.36</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>426</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.19221969</v>
+        <v>10.489998</v>
       </c>
       <c r="DR2" t="n">
-        <v>83.40000000000001</v>
+        <v>0.16301474</v>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
+          <t>64.35 - 117.9</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>-43.060005</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.3652248</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-19.742626</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1785511800</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1785511800</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1785511800</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1778068800</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1778068800</v>
+      </c>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-2.284401</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.029619692</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-7.827507</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.09468662999999999</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>HENSOLDT GmbH</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="EL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EN2" t="n">
+        <v>5.3194466</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>74.84</v>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
           <t>HENSOLDT</t>
         </is>
       </c>
-      <c r="DT2" t="n">
-        <v>0.16000366</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>81.0 - 81.0</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>309</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>19.050003</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.29603735</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>64.35 - 117.9</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>-34.5</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.29262087</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-17.665678</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1785511800</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1785511800</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1785511800</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1778068800</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1778068800</v>
-      </c>
-      <c r="EI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>6.2196045</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.08058528600000001</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.1453476</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.0017397449</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>HENSOLDT GmbH</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>1715756400000</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>4.0032</v>
+      <c r="EQ2" t="n">
+        <v>3.4174</v>
       </c>
     </row>
   </sheetData>
